--- a/artfynd/A 46634-2022 artfynd.xlsx
+++ b/artfynd/A 46634-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46634-2022 artfynd.xlsx
+++ b/artfynd/A 46634-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60800526</v>
+        <v>56179942</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>37</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; Broome) Bas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655869.1739344866</v>
+        <v>655832</v>
       </c>
       <c r="R2" t="n">
-        <v>6647685.719506329</v>
+        <v>6647730</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,24 +752,14 @@
           <t>2004-08-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2004-08-06</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ca. 20 ex.</t>
+          <t>1 ex. under ek, hassel och gran i mossrik granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,13 +768,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre granskog.</t>
+          <t>Mossrik granskog med inslag av lövträd och hassel.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,6 +788,123 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>60800526</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svartkärret 5 km VSV om Rasbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>655869</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6647686</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2004-08-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2004-08-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca. 20 ex.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
